--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DACC84-3D86-4B76-99D1-57FDAEB7C902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8348F86768B1671D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB85C50-D990-4F6A-AAA3-48B69F46C8BF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 14-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8348F86768B1671D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB85C50-D990-4F6A-AAA3-48B69F46C8BF}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8348D06F68FF870D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3CFC52-31EA-4142-97A2-136999930A0B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8348D06F68FF870D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3CFC52-31EA-4142-97A2-136999930A0B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D0D34B-E694-41A5-B1AA-9360A95A17A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D0D34B-E694-41A5-B1AA-9360A95A17A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AC86A4-6F80-48A6-88B5-3DB800C16AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 14-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 17-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AC86A4-6F80-48A6-88B5-3DB800C16AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD4B813-A32A-47AE-89F4-813E50F08A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD4B813-A32A-47AE-89F4-813E50F08A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8343F16B1BF7271D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECFE6D53-B1C0-4032-A715-F2C886F710BD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 17-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 21-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8343F16B1BF7271D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECFE6D53-B1C0-4032-A715-F2C886F710BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F051466C-B5A6-4C8A-91A0-60EA7DDF15F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F051466C-B5A6-4C8A-91A0-60EA7DDF15F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FA12E6-A057-409E-84EE-F3C277C0BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 21-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FA12E6-A057-409E-84EE-F3C277C0BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE9FFEF-9D9F-4F66-BE11-AFB1F0431D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE9FFEF-9D9F-4F66-BE11-AFB1F0431D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8349E7674A85871D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B568DE3-210F-4A1F-9964-9024A35FCC84}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 24-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8349E7674A85871D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B568DE3-210F-4A1F-9964-9024A35FCC84}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA099C37-D2B5-4EEB-AEFD-79F2A19AEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 24-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 28-09-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA099C37-D2B5-4EEB-AEFD-79F2A19AEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C83414EEF390E871D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B6547D1-0A8E-4609-98AA-97F9930989FD}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 28-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FA12E6-A057-409E-84EE-F3C277C0BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329C90B4-F91C-4588-ACC9-2DF558D1D977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 22-09-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 07-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C83414EEF390E871D8B027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B6547D1-0A8E-4609-98AA-97F9930989FD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6EBC61-249D-4594-B315-7C4C4DE9AD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 02-10-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 07-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -470,9 +470,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -548,7 +548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -605,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -619,7 +619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -682,7 +682,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -736,7 +736,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6EBC61-249D-4594-B315-7C4C4DE9AD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8341B0673ACFC71D8B023" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FF9ECB1-CB20-461A-8A8A-E809E8874566}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 07-10-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 08-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C8341B0673ACFC71D8B023" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FF9ECB1-CB20-461A-8A8A-E809E8874566}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56FF419-A666-4D8F-AC6E-64E9CFF182BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 08-10-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56FF419-A666-4D8F-AC6E-64E9CFF182BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE661768-B2DE-4084-A795-BD909082FE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/PRO-standarder (HL7 CDA)_excel.XLSX
+++ b/html/PRO-standarder (HL7 CDA)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE661768-B2DE-4084-A795-BD909082FE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9770D3FD4B7C834A92E76943A70D8B023" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADEFB5C4-F06E-4A59-A49E-19780E652BF4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 09-10-2026'!$A$1:$S$14</definedName>
+    <definedName name="PRO_standarder__HL7_CDA_">'Opdateret d. 23-10-2026'!$A$1:$S$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
